--- a/134_Cuenca_Camana/_raw_reportes_xlsx/IDConfig_65034_completo.xlsx
+++ b/134_Cuenca_Camana/_raw_reportes_xlsx/IDConfig_65034_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd2533c23f63c425d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R3ab628b548584760"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,516 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.7189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.7189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.7189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.7189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.7189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.7189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.7189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.7189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.7189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.7189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>15/08/2026</x:t>
         </x:is>
       </x:c>

--- a/134_Cuenca_Camana/_raw_reportes_xlsx/IDConfig_65034_completo.xlsx
+++ b/134_Cuenca_Camana/_raw_reportes_xlsx/IDConfig_65034_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R3ab628b548584760"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R52ddbe973151494d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,16 +255,2881 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>11/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.7506</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>24/08/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
         <x:is>
-          <x:t>10:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     31.7675</x:v>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -275,11 +3140,41 @@
       </x:c>
       <x:c s="7" t="inlineStr">
         <x:is>
-          <x:t>06:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     31.7675</x:v>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +3189,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +3204,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +3219,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +3234,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +3249,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +3264,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +3279,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +3294,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +3309,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +3324,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +3339,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +3354,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +3369,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +3384,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +3399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +3414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +3429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +3444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,7 +3459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +3474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,7 +3489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -609,7 +3504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -624,7 +3519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -639,7 +3534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -654,7 +3549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -669,7 +3564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -684,7 +3579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -699,7 +3594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -714,7 +3609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -729,7 +3624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -744,7 +3639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -759,7 +3654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -774,7 +3669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -789,7 +3684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -804,7 +3699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -819,7 +3714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -834,7 +3729,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -849,7 +3744,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -864,7 +3759,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -879,7 +3774,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -894,7 +3789,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -909,7 +3804,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -924,7 +3819,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -939,7 +3834,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -954,7 +3849,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -969,7 +3864,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -984,7 +3879,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -999,7 +3894,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1014,7 +3909,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1029,7 +3924,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1044,7 +3939,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1059,7 +3954,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1074,7 +3969,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1089,7 +3984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1104,7 +3999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1119,7 +4014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1134,7 +4029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1149,7 +4044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1164,7 +4059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1179,7 +4074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1194,7 +4089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1209,7 +4104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1224,7 +4119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1239,7 +4134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1254,7 +4149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1269,7 +4164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1284,7 +4179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1299,7 +4194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1314,7 +4209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1329,7 +4224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1344,7 +4239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1359,7 +4254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1374,7 +4269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1389,7 +4284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1404,7 +4299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1419,7 +4314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1434,7 +4329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1449,7 +4344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1464,7 +4359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1479,7 +4374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1494,7 +4389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1509,7 +4404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1524,7 +4419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1539,7 +4434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1554,7 +4449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1569,7 +4464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1584,7 +4479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1599,7 +4494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1614,7 +4509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1629,7 +4524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1644,7 +4539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1659,7 +4554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1674,7 +4569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1689,7 +4584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1704,7 +4599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1719,7 +4614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1734,7 +4629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1749,7 +4644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1764,7 +4659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1779,7 +4674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1794,7 +4689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1809,7 +4704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1824,7 +4719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1839,7 +4734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1854,7 +4749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1869,7 +4764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1884,7 +4779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1899,7 +4794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1914,7 +4809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1929,7 +4824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1944,7 +4839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1959,7 +4854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1974,7 +4869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1989,7 +4884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2004,7 +4899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2019,7 +4914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2034,7 +4929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2049,7 +4944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2064,7 +4959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2079,7 +4974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2094,7 +4989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2109,7 +5004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2124,7 +5019,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2139,7 +5034,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2154,7 +5049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2169,7 +5064,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2184,7 +5079,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2199,7 +5094,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2214,7 +5109,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2229,7 +5124,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2244,7 +5139,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2259,7 +5154,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2274,7 +5169,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2289,7 +5184,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2304,7 +5199,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2319,7 +5214,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2334,7 +5229,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2349,7 +5244,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2364,7 +5259,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2379,7 +5274,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2394,7 +5289,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2409,7 +5304,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2424,7 +5319,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2439,7 +5334,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2454,7 +5349,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2469,7 +5364,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2484,7 +5379,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2499,7 +5394,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2514,7 +5409,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2529,7 +5424,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2544,7 +5439,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2559,7 +5454,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2574,7 +5469,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2589,7 +5484,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2604,7 +5499,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2619,7 +5514,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2634,7 +5529,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2649,7 +5544,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2664,7 +5559,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2679,7 +5574,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2694,7 +5589,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.5245</x:v>
+        <x:v>     35.5624</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2709,7 +5604,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2724,7 +5619,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.5245</x:v>
+        <x:v>     35.5624</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2739,7 +5634,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.5245</x:v>
+        <x:v>     35.5624</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2754,7 +5649,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.5245</x:v>
+        <x:v>     35.5624</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2769,7 +5664,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.5245</x:v>
+        <x:v>     35.5624</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2784,7 +5679,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.5245</x:v>
+        <x:v>     35.5624</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2799,7 +5694,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.5245</x:v>
+        <x:v>     35.5624</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2814,7 +5709,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.5245</x:v>
+        <x:v>     35.5624</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2829,7 +5724,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.5245</x:v>
+        <x:v>     35.5624</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2844,7 +5739,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.5245</x:v>
+        <x:v>     35.5624</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2859,7 +5754,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.5245</x:v>
+        <x:v>     35.5624</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2874,7 +5769,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.5245</x:v>
+        <x:v>     35.5624</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2889,7 +5784,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.5245</x:v>
+        <x:v>     35.5624</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2904,7 +5799,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2919,7 +5814,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2934,7 +5829,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2949,7 +5844,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2964,7 +5859,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2979,7 +5874,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2994,7 +5889,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3009,7 +5904,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.3786</x:v>
+        <x:v>     38.4818</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3024,7 +5919,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.3786</x:v>
+        <x:v>     38.4818</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3039,7 +5934,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.3786</x:v>
+        <x:v>     38.4818</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3054,7 +5949,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.3786</x:v>
+        <x:v>     38.4818</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3069,7 +5964,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.3786</x:v>
+        <x:v>     38.4818</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3084,7 +5979,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3099,7 +5994,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.5245</x:v>
+        <x:v>     35.5624</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3114,7 +6009,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3129,7 +6024,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.5245</x:v>
+        <x:v>     35.5624</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3144,7 +6039,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3159,7 +6054,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3174,7 +6069,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3189,7 +6084,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3204,7 +6099,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3219,7 +6114,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3234,7 +6129,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3249,7 +6144,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3264,7 +6159,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3279,7 +6174,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3294,7 +6189,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3309,7 +6204,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3324,7 +6219,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3339,7 +6234,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3354,7 +6249,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3369,7 +6264,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3384,7 +6279,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3399,7 +6294,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3414,7 +6309,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3429,7 +6324,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3444,7 +6339,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3459,7 +6354,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3474,7 +6369,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3489,7 +6384,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3504,7 +6399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3519,7 +6414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3534,7 +6429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3549,7 +6444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3564,7 +6459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3579,7 +6474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3594,7 +6489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3609,7 +6504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3624,7 +6519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3639,7 +6534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3654,7 +6549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3669,7 +6564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3684,7 +6579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3699,7 +6594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3714,7 +6609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3729,7 +6624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3744,7 +6639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3759,7 +6654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3774,7 +6669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3789,7 +6684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3804,7 +6699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3819,7 +6714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3834,7 +6729,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3849,7 +6744,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3864,7 +6759,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3879,7 +6774,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3894,7 +6789,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3909,7 +6804,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3924,7 +6819,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3939,7 +6834,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3954,7 +6849,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3969,7 +6864,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3984,7 +6879,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3999,7 +6894,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4014,7 +6909,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4029,7 +6924,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4044,7 +6939,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4059,7 +6954,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4074,7 +6969,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4089,7 +6984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4104,7 +6999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4119,7 +7014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4134,7 +7029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4149,7 +7044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4164,7 +7059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4179,7 +7074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4194,7 +7089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4209,7 +7104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4224,7 +7119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4239,7 +7134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4254,7 +7149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4269,7 +7164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4284,7 +7179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4299,7 +7194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4314,7 +7209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4329,7 +7224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4344,7 +7239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4359,7 +7254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4374,7 +7269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4389,7 +7284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4404,7 +7299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4419,7 +7314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4434,7 +7329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4449,7 +7344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4464,7 +7359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.3786</x:v>
+        <x:v>     38.4818</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4479,7 +7374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.3786</x:v>
+        <x:v>     38.4818</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4494,7 +7389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.3786</x:v>
+        <x:v>     38.4818</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4509,7 +7404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.3786</x:v>
+        <x:v>     38.4818</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4524,7 +7419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.3786</x:v>
+        <x:v>     38.4818</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4539,7 +7434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.3786</x:v>
+        <x:v>     38.4818</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4554,7 +7449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.3786</x:v>
+        <x:v>     38.4818</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4569,7 +7464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.3786</x:v>
+        <x:v>     38.4818</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4584,7 +7479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.3300</x:v>
+        <x:v>     39.4549</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4599,7 +7494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.3300</x:v>
+        <x:v>     39.4549</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4614,7 +7509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.3300</x:v>
+        <x:v>     39.4549</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4629,7 +7524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.3300</x:v>
+        <x:v>     39.4549</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4644,7 +7539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.3300</x:v>
+        <x:v>     39.4549</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4659,7 +7554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.3300</x:v>
+        <x:v>     39.4549</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4674,7 +7569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.3300</x:v>
+        <x:v>     39.4549</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4689,7 +7584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.3300</x:v>
+        <x:v>     39.4549</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4704,7 +7599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.3300</x:v>
+        <x:v>     39.4549</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4719,7 +7614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.3300</x:v>
+        <x:v>     39.4549</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4734,7 +7629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.3300</x:v>
+        <x:v>     39.4549</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4749,7 +7644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.3300</x:v>
+        <x:v>     39.4549</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4764,7 +7659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.3300</x:v>
+        <x:v>     39.4549</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4779,7 +7674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.3300</x:v>
+        <x:v>     39.4549</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4794,7 +7689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.2814</x:v>
+        <x:v>     40.4280</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4809,7 +7704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.2814</x:v>
+        <x:v>     40.4280</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4824,7 +7719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.2814</x:v>
+        <x:v>     40.4280</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4839,7 +7734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.2814</x:v>
+        <x:v>     40.4280</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4854,7 +7749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.2814</x:v>
+        <x:v>     40.4280</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4869,7 +7764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.2814</x:v>
+        <x:v>     40.4280</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4884,7 +7779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.2814</x:v>
+        <x:v>     40.4280</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4899,7 +7794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     43.1842</x:v>
+        <x:v>     42.3742</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4914,7 +7809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     43.1842</x:v>
+        <x:v>     42.3742</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4929,7 +7824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     43.1842</x:v>
+        <x:v>     42.3742</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4944,7 +7839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     43.1842</x:v>
+        <x:v>     42.3742</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4959,7 +7854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4974,7 +7869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4989,7 +7884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5004,7 +7899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5019,7 +7914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5034,7 +7929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5049,7 +7944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5064,7 +7959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5079,7 +7974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5094,7 +7989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5109,7 +8004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5124,7 +8019,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5139,7 +8034,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5154,7 +8049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5169,7 +8064,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5184,7 +8079,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5199,7 +8094,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5214,7 +8109,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5229,7 +8124,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5244,7 +8139,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5259,7 +8154,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5274,7 +8169,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5289,7 +8184,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5304,7 +8199,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5319,7 +8214,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5334,7 +8229,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5349,7 +8244,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5364,7 +8259,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5379,7 +8274,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5394,7 +8289,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5409,7 +8304,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5424,7 +8319,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5439,7 +8334,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5454,7 +8349,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5469,7 +8364,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5484,7 +8379,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5499,7 +8394,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5514,7 +8409,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5529,7 +8424,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5544,7 +8439,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5559,7 +8454,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5574,7 +8469,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5589,7 +8484,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5604,7 +8499,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5619,7 +8514,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5634,7 +8529,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5649,7 +8544,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5664,7 +8559,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5679,7 +8574,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5694,7 +8589,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5709,7 +8604,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5724,7 +8619,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5739,7 +8634,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5754,7 +8649,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5769,7 +8664,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5784,7 +8679,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5799,7 +8694,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5814,7 +8709,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5829,7 +8724,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5844,7 +8739,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5859,7 +8754,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5874,7 +8769,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5889,7 +8784,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5904,7 +8799,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5919,7 +8814,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5934,7 +8829,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5949,7 +8844,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5964,7 +8859,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5979,7 +8874,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5994,7 +8889,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6009,7 +8904,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6024,7 +8919,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6039,7 +8934,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6054,7 +8949,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6069,7 +8964,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6084,7 +8979,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6099,7 +8994,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6114,7 +9009,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6129,7 +9024,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6144,7 +9039,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6159,7 +9054,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6174,7 +9069,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6189,7 +9084,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6204,7 +9099,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6219,7 +9114,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6234,7 +9129,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6249,7 +9144,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6264,7 +9159,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6279,7 +9174,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6294,7 +9189,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6309,7 +9204,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6324,7 +9219,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6339,7 +9234,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6354,7 +9249,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6369,7 +9264,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6384,7 +9279,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6399,7 +9294,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6414,7 +9309,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6429,7 +9324,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6444,7 +9339,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6459,7 +9354,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6474,7 +9369,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6489,7 +9384,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6504,7 +9399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6519,7 +9414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6534,7 +9429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6549,7 +9444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6564,7 +9459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6579,7 +9474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6594,7 +9489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6609,7 +9504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6624,7 +9519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6639,7 +9534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6654,7 +9549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6669,7 +9564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6684,7 +9579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6699,7 +9594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6714,7 +9609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6729,7 +9624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6744,7 +9639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6759,7 +9654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6774,7 +9669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.9898</x:v>
+        <x:v>     46.2667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6789,7 +9684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6804,7 +9699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.9898</x:v>
+        <x:v>     46.2667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6819,7 +9714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.9898</x:v>
+        <x:v>     46.2667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6834,7 +9729,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.9898</x:v>
+        <x:v>     46.2667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6849,7 +9744,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.9898</x:v>
+        <x:v>     46.2667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6864,7 +9759,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.9898</x:v>
+        <x:v>     46.2667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6879,7 +9774,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.9412</x:v>
+        <x:v>     47.2398</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6894,7 +9789,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.9898</x:v>
+        <x:v>     46.2667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6909,7 +9804,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.9898</x:v>
+        <x:v>     46.2667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6924,7 +9819,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.8926</x:v>
+        <x:v>     48.2130</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6939,7 +9834,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.8926</x:v>
+        <x:v>     48.2130</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6954,7 +9849,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6969,7 +9864,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6984,7 +9879,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     50.7954</x:v>
+        <x:v>     50.1592</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6999,7 +9894,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     50.7954</x:v>
+        <x:v>     50.1592</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7014,7 +9909,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7029,7 +9924,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7044,7 +9939,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     50.7954</x:v>
+        <x:v>     50.1592</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7059,7 +9954,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     50.7954</x:v>
+        <x:v>     50.1592</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7074,7 +9969,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.7468</x:v>
+        <x:v>     51.1323</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7089,7 +9984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.7468</x:v>
+        <x:v>     51.1323</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7104,7 +9999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.6982</x:v>
+        <x:v>     52.1054</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7119,7 +10014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.6982</x:v>
+        <x:v>     52.1054</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7134,7 +10029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     53.6496</x:v>
+        <x:v>     53.0785</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7149,7 +10044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     53.6496</x:v>
+        <x:v>     53.0785</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7164,7 +10059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     53.6496</x:v>
+        <x:v>     53.0785</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7179,7 +10074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.6010</x:v>
+        <x:v>     54.0517</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7194,7 +10089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     56.5037</x:v>
+        <x:v>     55.9979</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7209,7 +10104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     56.5037</x:v>
+        <x:v>     55.9979</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7224,7 +10119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     56.5037</x:v>
+        <x:v>     55.9979</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7239,7 +10134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     57.4551</x:v>
+        <x:v>     56.9710</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7254,7 +10149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     63.1635</x:v>
+        <x:v>     62.8097</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7269,7 +10164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     63.1635</x:v>
+        <x:v>     62.8097</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7284,7 +10179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.2607</x:v>
+        <x:v>     60.8635</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7299,7 +10194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.2607</x:v>
+        <x:v>     60.8635</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7314,7 +10209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     68.8719</x:v>
+        <x:v>     68.6484</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7329,7 +10224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     67.9205</x:v>
+        <x:v>     67.6753</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7344,7 +10239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     68.8719</x:v>
+        <x:v>     68.6484</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7359,7 +10254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     67.9205</x:v>
+        <x:v>     67.6753</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7374,7 +10269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     65.0663</x:v>
+        <x:v>     64.7559</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7389,7 +10284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     66.0177</x:v>
+        <x:v>     65.7291</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7404,7 +10299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     67.9205</x:v>
+        <x:v>     67.6753</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7419,7 +10314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     68.8719</x:v>
+        <x:v>     68.6484</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7434,7 +10329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     67.9205</x:v>
+        <x:v>     67.6753</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7449,7 +10344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     68.8719</x:v>
+        <x:v>     68.6484</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7464,7 +10359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     73.6289</x:v>
+        <x:v>     73.5140</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7479,7 +10374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     73.6289</x:v>
+        <x:v>     73.5140</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7494,7 +10389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     74.5803</x:v>
+        <x:v>     74.4871</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7509,7 +10404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     75.5316</x:v>
+        <x:v>     75.4602</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7524,7 +10419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     78.3858</x:v>
+        <x:v>     78.3796</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7554,7 +10449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     76.4830</x:v>
+        <x:v>     76.4333</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7569,7 +10464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     74.5803</x:v>
+        <x:v>     74.4871</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7584,7 +10479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     73.6289</x:v>
+        <x:v>     73.5140</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7599,7 +10494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     72.6775</x:v>
+        <x:v>     72.5409</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7614,7 +10509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     75.5316</x:v>
+        <x:v>     75.4602</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7629,7 +10524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     76.4830</x:v>
+        <x:v>     76.4333</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7644,7 +10539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.2886</x:v>
+        <x:v>     80.3258</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7659,7 +10554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     78.3858</x:v>
+        <x:v>     78.3796</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7674,7 +10569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     64.1149</x:v>
+        <x:v>     63.7828</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7689,7 +10584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     58.4065</x:v>
+        <x:v>     57.9441</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7704,7 +10599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     56.5037</x:v>
+        <x:v>     55.9979</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7719,7 +10614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     57.4551</x:v>
+        <x:v>     56.9710</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7734,7 +10629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     55.5524</x:v>
+        <x:v>     55.0248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7749,7 +10644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     55.5524</x:v>
+        <x:v>     55.0248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7764,7 +10659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     55.5524</x:v>
+        <x:v>     55.0248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7779,7 +10674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     56.5037</x:v>
+        <x:v>     55.9979</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7794,7 +10689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.6010</x:v>
+        <x:v>     54.0517</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7809,7 +10704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.6010</x:v>
+        <x:v>     54.0517</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7824,7 +10719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     55.5524</x:v>
+        <x:v>     55.0248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7839,7 +10734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.6010</x:v>
+        <x:v>     54.0517</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7854,7 +10749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.7468</x:v>
+        <x:v>     51.1323</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7869,7 +10764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.6982</x:v>
+        <x:v>     52.1054</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7884,7 +10779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.6982</x:v>
+        <x:v>     52.1054</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7899,7 +10794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     53.6496</x:v>
+        <x:v>     53.0785</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7914,7 +10809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.6010</x:v>
+        <x:v>     54.0517</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7929,7 +10824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.6010</x:v>
+        <x:v>     54.0517</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7944,7 +10839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     55.5524</x:v>
+        <x:v>     55.0248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7959,7 +10854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     57.4551</x:v>
+        <x:v>     56.9710</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7974,7 +10869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     60.3093</x:v>
+        <x:v>     59.8904</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7989,7 +10884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     60.3093</x:v>
+        <x:v>     59.8904</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8004,7 +10899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     58.4065</x:v>
+        <x:v>     57.9441</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8019,7 +10914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     60.3093</x:v>
+        <x:v>     59.8904</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8034,7 +10929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     62.2121</x:v>
+        <x:v>     61.8366</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8049,7 +10944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     63.1635</x:v>
+        <x:v>     62.8097</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8064,7 +10959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     63.1635</x:v>
+        <x:v>     62.8097</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8079,7 +10974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     64.1149</x:v>
+        <x:v>     63.7828</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8094,7 +10989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     70.7747</x:v>
+        <x:v>     70.5946</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8109,7 +11004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     70.7747</x:v>
+        <x:v>     70.5946</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8124,7 +11019,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     71.7261</x:v>
+        <x:v>     71.5678</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8139,7 +11034,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     71.7261</x:v>
+        <x:v>     71.5678</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8154,7 +11049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     73.6289</x:v>
+        <x:v>     73.5140</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8169,7 +11064,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     72.6775</x:v>
+        <x:v>     72.5409</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8184,7 +11079,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     73.6289</x:v>
+        <x:v>     73.5140</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8199,7 +11094,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     73.6289</x:v>
+        <x:v>     73.5140</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8214,7 +11109,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     70.7747</x:v>
+        <x:v>     70.5946</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8229,7 +11124,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     70.7747</x:v>
+        <x:v>     70.5946</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8244,7 +11139,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     70.7747</x:v>
+        <x:v>     70.5946</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8259,7 +11154,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     70.7747</x:v>
+        <x:v>     70.5946</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8274,7 +11169,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     73.6289</x:v>
+        <x:v>     73.5140</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8289,7 +11184,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     74.5803</x:v>
+        <x:v>     74.4871</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8304,7 +11199,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     75.5316</x:v>
+        <x:v>     75.4602</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8319,7 +11214,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     75.5316</x:v>
+        <x:v>     75.4602</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9444,7 +12339,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     66.0177</x:v>
+        <x:v>     65.7291</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9459,7 +12354,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     64.1149</x:v>
+        <x:v>     63.7828</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9474,7 +12369,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     59.3579</x:v>
+        <x:v>     58.9172</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9489,7 +12384,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.6010</x:v>
+        <x:v>     54.0517</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9504,7 +12399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     53.6496</x:v>
+        <x:v>     53.0785</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9519,7 +12414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     53.6496</x:v>
+        <x:v>     53.0785</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9534,7 +12429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.7468</x:v>
+        <x:v>     51.1323</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9549,7 +12444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.7468</x:v>
+        <x:v>     51.1323</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9564,7 +12459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.7468</x:v>
+        <x:v>     51.1323</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9579,7 +12474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.7468</x:v>
+        <x:v>     51.1323</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9594,7 +12489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.7468</x:v>
+        <x:v>     51.1323</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9609,7 +12504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.6982</x:v>
+        <x:v>     52.1054</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9624,7 +12519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.6982</x:v>
+        <x:v>     52.1054</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9639,7 +12534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.6982</x:v>
+        <x:v>     52.1054</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9654,7 +12549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.6982</x:v>
+        <x:v>     52.1054</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9669,7 +12564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.6982</x:v>
+        <x:v>     52.1054</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9684,7 +12579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.6982</x:v>
+        <x:v>     52.1054</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9699,7 +12594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     53.6496</x:v>
+        <x:v>     53.0785</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9714,7 +12609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9729,7 +12624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9744,7 +12639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     50.7954</x:v>
+        <x:v>     50.1592</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9759,7 +12654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     50.7954</x:v>
+        <x:v>     50.1592</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9774,7 +12669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.8926</x:v>
+        <x:v>     48.2130</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9789,7 +12684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9804,7 +12699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     50.7954</x:v>
+        <x:v>     50.1592</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9819,7 +12714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     50.7954</x:v>
+        <x:v>     50.1592</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9834,7 +12729,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9849,7 +12744,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9864,7 +12759,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     50.7954</x:v>
+        <x:v>     50.1592</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9879,7 +12774,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     50.7954</x:v>
+        <x:v>     50.1592</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9894,7 +12789,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9909,7 +12804,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9924,7 +12819,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9939,7 +12834,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9954,7 +12849,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.8926</x:v>
+        <x:v>     48.2130</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9969,7 +12864,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.8926</x:v>
+        <x:v>     48.2130</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9984,7 +12879,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.8926</x:v>
+        <x:v>     48.2130</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9999,7 +12894,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.7468</x:v>
+        <x:v>     51.1323</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10014,7 +12909,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     50.7954</x:v>
+        <x:v>     50.1592</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10029,7 +12924,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.7468</x:v>
+        <x:v>     51.1323</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10044,7 +12939,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.6982</x:v>
+        <x:v>     52.1054</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10059,7 +12954,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.6982</x:v>
+        <x:v>     52.1054</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10074,7 +12969,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.7468</x:v>
+        <x:v>     51.1323</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10089,7 +12984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.6982</x:v>
+        <x:v>     52.1054</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10104,7 +12999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.6010</x:v>
+        <x:v>     54.0517</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10119,7 +13014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.6010</x:v>
+        <x:v>     54.0517</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10134,7 +13029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.8926</x:v>
+        <x:v>     48.2130</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10149,7 +13044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.8926</x:v>
+        <x:v>     48.2130</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10164,7 +13059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10179,7 +13074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10194,7 +13089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.9412</x:v>
+        <x:v>     47.2398</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10209,7 +13104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.9412</x:v>
+        <x:v>     47.2398</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10224,7 +13119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.9412</x:v>
+        <x:v>     47.2398</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10239,7 +13134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.8926</x:v>
+        <x:v>     48.2130</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10254,7 +13149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.9412</x:v>
+        <x:v>     47.2398</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10269,7 +13164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.9412</x:v>
+        <x:v>     47.2398</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10284,7 +13179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10299,7 +13194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10314,7 +13209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.9412</x:v>
+        <x:v>     47.2398</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10329,7 +13224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.9412</x:v>
+        <x:v>     47.2398</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10344,7 +13239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.8926</x:v>
+        <x:v>     48.2130</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10359,7 +13254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10374,7 +13269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     50.7954</x:v>
+        <x:v>     50.1592</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10389,7 +13284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     50.7954</x:v>
+        <x:v>     50.1592</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10404,7 +13299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10419,7 +13314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10434,7 +13329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10449,7 +13344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10464,7 +13359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10479,7 +13374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10494,7 +13389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.8926</x:v>
+        <x:v>     48.2130</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10509,7 +13404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.8926</x:v>
+        <x:v>     48.2130</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10524,7 +13419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     50.7954</x:v>
+        <x:v>     50.1592</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10539,7 +13434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     50.7954</x:v>
+        <x:v>     50.1592</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10554,7 +13449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10569,7 +13464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10584,7 +13479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     50.7954</x:v>
+        <x:v>     50.1592</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10599,7 +13494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.7468</x:v>
+        <x:v>     51.1323</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10614,7 +13509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.7468</x:v>
+        <x:v>     51.1323</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10629,7 +13524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     53.6496</x:v>
+        <x:v>     53.0785</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10644,7 +13539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.6010</x:v>
+        <x:v>     54.0517</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10659,7 +13554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.6010</x:v>
+        <x:v>     54.0517</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10674,7 +13569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.6010</x:v>
+        <x:v>     54.0517</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10689,7 +13584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.6010</x:v>
+        <x:v>     54.0517</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10704,7 +13599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     55.5524</x:v>
+        <x:v>     55.0248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10719,7 +13614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     58.4065</x:v>
+        <x:v>     57.9441</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10734,7 +13629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     58.4065</x:v>
+        <x:v>     57.9441</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10749,7 +13644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     59.3579</x:v>
+        <x:v>     58.9172</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10764,7 +13659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     60.3093</x:v>
+        <x:v>     59.8904</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10779,7 +13674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.2607</x:v>
+        <x:v>     60.8635</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10794,7 +13689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     65.0663</x:v>
+        <x:v>     64.7559</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10809,7 +13704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     66.9691</x:v>
+        <x:v>     66.7022</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10824,7 +13719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     67.9205</x:v>
+        <x:v>     67.6753</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10839,7 +13734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.2886</x:v>
+        <x:v>     80.3258</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10854,7 +13749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     79.3372</x:v>
+        <x:v>     79.3527</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10869,7 +13764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     79.3372</x:v>
+        <x:v>     79.3527</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11874,7 +14769,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     79.3372</x:v>
+        <x:v>     79.3527</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11889,7 +14784,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.2886</x:v>
+        <x:v>     80.3258</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12714,7 +15609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     73.6289</x:v>
+        <x:v>     73.5140</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12729,7 +15624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     53.6496</x:v>
+        <x:v>     53.0785</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12744,7 +15639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     73.6289</x:v>
+        <x:v>     73.5140</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12759,7 +15654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     74.5803</x:v>
+        <x:v>     74.4871</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12774,7 +15669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     68.8719</x:v>
+        <x:v>     68.6484</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12789,7 +15684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     68.8719</x:v>
+        <x:v>     68.6484</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12804,7 +15699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     69.8233</x:v>
+        <x:v>     69.6215</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12819,7 +15714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     74.5803</x:v>
+        <x:v>     74.4871</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12834,7 +15729,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.2886</x:v>
+        <x:v>     80.3258</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13134,7 +16029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.9412</x:v>
+        <x:v>     47.2398</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13149,7 +16044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     55.5524</x:v>
+        <x:v>     55.0248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13164,7 +16059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     59.3579</x:v>
+        <x:v>     58.9172</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13179,7 +16074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     59.3579</x:v>
+        <x:v>     58.9172</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13194,7 +16089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     56.5037</x:v>
+        <x:v>     55.9979</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13209,7 +16104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     58.4065</x:v>
+        <x:v>     57.9441</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13224,7 +16119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     62.2121</x:v>
+        <x:v>     61.8366</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13239,7 +16134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     59.3579</x:v>
+        <x:v>     58.9172</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13254,7 +16149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     50.7954</x:v>
+        <x:v>     50.1592</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13269,7 +16164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.5245</x:v>
+        <x:v>     35.5624</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13284,7 +16179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.3786</x:v>
+        <x:v>     38.4818</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13299,7 +16194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.2814</x:v>
+        <x:v>     40.4280</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13314,7 +16209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13329,7 +16224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13344,7 +16239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13359,7 +16254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13374,7 +16269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13389,7 +16284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13404,7 +16299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13419,7 +16314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13434,7 +16329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13449,7 +16344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13464,7 +16359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13479,7 +16374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.5245</x:v>
+        <x:v>     35.5624</x:v>
       </x:c>
     </x:row>
     <x:row>
